--- a/public/samples/royalty_performance_deduction_sample.xlsx
+++ b/public/samples/royalty_performance_deduction_sample.xlsx
@@ -72,9 +72,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:C5"/>
   <sheetData>
-    <row r="1" spans="1:6" customHeight="0">
+    <row r="1" spans="1:3" customHeight="0">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Employee Code</t>
@@ -82,31 +82,16 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Employee Name</t>
+          <t>Percentage</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Department</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Designation</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Performance Deduction %</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Remarks / Reason</t>
+          <t>Remarks</t>
         </is>
       </c>
     </row>
-    <row r="2" spans="1:6" customHeight="0">
+    <row r="2" spans="1:3" customHeight="0">
       <c r="A2" s="0" t="inlineStr">
         <is>
           <t>EMP001</t>
@@ -114,31 +99,16 @@
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>John Doe</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
         <is>
-          <t>Gaming</t>
-        </is>
-      </c>
-      <c r="D2" s="0" t="inlineStr">
-        <is>
-          <t>Dealer</t>
-        </is>
-      </c>
-      <c r="E2" s="0" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="F2" s="0" t="inlineStr">
-        <is>
-          <t>Met all monthly KPIs</t>
+          <t>Late submission of monthly deliverables</t>
         </is>
       </c>
     </row>
-    <row r="3" spans="1:6" customHeight="0">
+    <row r="3" spans="1:3" customHeight="0">
       <c r="A3" s="0" t="inlineStr">
         <is>
           <t>EMP002</t>
@@ -146,31 +116,16 @@
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t>Jane Smith</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="C3" s="0" t="inlineStr">
         <is>
-          <t>Food &amp; Beverage</t>
-        </is>
-      </c>
-      <c r="D3" s="0" t="inlineStr">
-        <is>
-          <t>Waiter</t>
-        </is>
-      </c>
-      <c r="E3" s="0" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="F3" s="0" t="inlineStr">
-        <is>
-          <t>Monthly KPI shortfall (-10%)</t>
+          <t>Monthly KPI shortfall (-15%)</t>
         </is>
       </c>
     </row>
-    <row r="4" spans="1:6" customHeight="0">
+    <row r="4" spans="1:3" customHeight="0">
       <c r="A4" s="0" t="inlineStr">
         <is>
           <t>EMP003</t>
@@ -178,31 +133,16 @@
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t>Ram Bahadur</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t>Housekeeping</t>
-        </is>
-      </c>
-      <c r="D4" s="0" t="inlineStr">
-        <is>
-          <t>Attendant</t>
-        </is>
-      </c>
-      <c r="E4" s="0" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="F4" s="0" t="inlineStr">
-        <is>
-          <t>Service quality escalation (-25%)</t>
+          <t>Service escalation penalty (-25%)</t>
         </is>
       </c>
     </row>
-    <row r="5" spans="1:6" customHeight="0">
+    <row r="5" spans="1:3" customHeight="0">
       <c r="A5" s="0" t="inlineStr">
         <is>
           <t>EMP004</t>
@@ -210,59 +150,12 @@
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t>Sita Sharma</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>Surveillance</t>
-        </is>
-      </c>
-      <c r="D5" s="0" t="inlineStr">
-        <is>
-          <t>Operator</t>
-        </is>
-      </c>
-      <c r="E5" s="0" t="inlineStr">
-        <is>
-          <t>15%</t>
-        </is>
-      </c>
-      <c r="F5" s="0" t="inlineStr">
-        <is>
-          <t>SOP compliance penalty (-15%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" spans="1:6" customHeight="0">
-      <c r="A6" s="0" t="inlineStr">
-        <is>
-          <t>EMP005</t>
-        </is>
-      </c>
-      <c r="B6" s="0" t="inlineStr">
-        <is>
-          <t>Hari Thapa</t>
-        </is>
-      </c>
-      <c r="C6" s="0" t="inlineStr">
-        <is>
-          <t>Security</t>
-        </is>
-      </c>
-      <c r="D6" s="0" t="inlineStr">
-        <is>
-          <t>Security Guard</t>
-        </is>
-      </c>
-      <c r="E6" s="0" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="F6" s="0" t="inlineStr">
-        <is>
-          <t>Clean performance record</t>
+          <t>Uniform &amp; grooming policy non-compliance</t>
         </is>
       </c>
     </row>
